--- a/routes-planning.xlsx
+++ b/routes-planning.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="80" windowWidth="19140" windowHeight="7340" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="80" windowWidth="19140" windowHeight="7340"/>
   </bookViews>
   <sheets>
     <sheet name="Rules" sheetId="1" r:id="rId1"/>
